--- a/skills/product-backlog/templates/ISC_FTI-FCR_v1.7_Product-Backlog_v1.0_20260731.xlsx
+++ b/skills/product-backlog/templates/ISC_FTI-FCR_v1.7_Product-Backlog_v1.0_20260731.xlsx
@@ -56,484 +56,484 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="240">
   <si>
-    <t xml:space="preserve">FTI-FCR</t>
+    <t>FTI-FCR</t>
   </si>
   <si>
-    <t xml:space="preserve">PRODUCT BACKLOG</t>
+    <t>PRODUCT BACKLOG</t>
   </si>
   <si>
-    <t xml:space="preserve">Mã hiệu</t>
+    <t>Mã hiệu</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0-BM/PM/HDCV/ISC</t>
+    <t>3.0-BM/PM/HDCV/ISC</t>
   </si>
   <si>
-    <t xml:space="preserve">Phiên bản</t>
+    <t>Phiên bản</t>
   </si>
   <si>
-    <t xml:space="preserve">1/0</t>
+    <t>1/0</t>
   </si>
   <si>
-    <t xml:space="preserve">STORY MAPPING</t>
+    <t>STORY MAPPING</t>
   </si>
   <si>
-    <t xml:space="preserve">[Ví dụ mang tính chất tham khảo, tùy size dự án có thể customize cho phù hợp]</t>
+    <t>[Ví dụ mang tính chất tham khảo, tùy size dự án có thể customize cho phù hợp]</t>
   </si>
   <si>
-    <t xml:space="preserve">PRODUCT BACKLOG - PROJECT</t>
+    <t>PRODUCT BACKLOG - PROJECT</t>
   </si>
   <si>
-    <t xml:space="preserve">PRODUCT/PROJECT NAME</t>
+    <t>PRODUCT/PROJECT NAME</t>
   </si>
   <si>
-    <t xml:space="preserve">A slicer is in cells H3 through I5. To filter inventory list by Photo, select Yes or No from the slicer in this cell.</t>
+    <t>A slicer is in cells H3 through I5. To filter inventory list by Photo, select Yes or No from the slicer in this cell.</t>
   </si>
   <si>
-    <t xml:space="preserve">KEY PO</t>
+    <t>KEY PO</t>
   </si>
   <si>
-    <t xml:space="preserve">QuanNT36</t>
+    <t>QuanNT36</t>
   </si>
   <si>
-    <t xml:space="preserve">DIVISION</t>
+    <t>DIVISION</t>
   </si>
   <si>
-    <t xml:space="preserve">FTI</t>
+    <t>FTI</t>
   </si>
   <si>
     <t xml:space="preserve">DOMAIN </t>
   </si>
   <si>
-    <t xml:space="preserve">Quản lý quy trình</t>
+    <t>Quản lý quy trình</t>
   </si>
   <si>
-    <t xml:space="preserve">Giới thiệu chung</t>
+    <t>Giới thiệu chung</t>
   </si>
   <si>
-    <t xml:space="preserve">Hoàn thiện và mở rộng hệ thống FCR, hướng tới số hóa quy trình, giảm thao tác thủ công, tăng khả năng xử lý linh hoạt và minh bạch cho các nghiệp vụ hợp đồng, dịch vụ và báo cáo</t>
+    <t>Hoàn thiện và mở rộng hệ thống FCR, hướng tới số hóa quy trình, giảm thao tác thủ công, tăng khả năng xử lý linh hoạt và minh bạch cho các nghiệp vụ hợp đồng, dịch vụ và báo cáo</t>
   </si>
   <si>
-    <t xml:space="preserve">Phạm vi triển khai</t>
+    <t>Phạm vi triển khai</t>
   </si>
   <si>
-    <t xml:space="preserve">Bao gồm các nghiệp vụ thanh lý, tạm ngưng, gia hạn, nâng cấp/hạ cấp, chuyển địa điểm, chuyển pháp nhân, xử lý yêu cầu nghiệp vụ, báo cáo và tích hợp liên thông giữa FCR, SM, CM và các tool dịch vụ liên quan</t>
+    <t>Bao gồm các nghiệp vụ thanh lý, tạm ngưng, gia hạn, nâng cấp/hạ cấp, chuyển địa điểm, chuyển pháp nhân, xử lý yêu cầu nghiệp vụ, báo cáo và tích hợp liên thông giữa FCR, SM, CM và các tool dịch vụ liên quan</t>
   </si>
   <si>
-    <t xml:space="preserve">PLATFORM</t>
+    <t>PLATFORM</t>
   </si>
   <si>
-    <t xml:space="preserve">Web</t>
+    <t>Web</t>
   </si>
   <si>
-    <t xml:space="preserve">Link Staging</t>
+    <t>Link Staging</t>
   </si>
   <si>
-    <t xml:space="preserve">https://ftms-stag.fpt.net/fcr</t>
+    <t>https://ftms-stag.fpt.net/fcr</t>
   </si>
   <si>
-    <t xml:space="preserve">Link Production</t>
+    <t>Link Production</t>
   </si>
   <si>
-    <t xml:space="preserve">https://ftms.fpt.net/fcr</t>
+    <t>https://ftms.fpt.net/fcr</t>
   </si>
   <si>
-    <t xml:space="preserve">Roadmap</t>
+    <t>Roadmap</t>
   </si>
   <si>
-    <t xml:space="preserve">NO.</t>
+    <t>NO.</t>
   </si>
   <si>
-    <t xml:space="preserve">REQUEST DATE</t>
+    <t>REQUEST DATE</t>
   </si>
   <si>
-    <t xml:space="preserve">EPICS/ITEMS</t>
+    <t>EPICS/ITEMS</t>
   </si>
   <si>
-    <t xml:space="preserve">MODULE/FEATURE</t>
+    <t>MODULE/FEATURE</t>
   </si>
   <si>
-    <t xml:space="preserve">USER STORY/DESCRIPTION</t>
+    <t>USER STORY/DESCRIPTION</t>
   </si>
   <si>
-    <t xml:space="preserve">PRIORITY</t>
+    <t>PRIORITY</t>
   </si>
   <si>
-    <t xml:space="preserve">SPRINT BACKLOG/VERSION</t>
+    <t>SPRINT BACKLOG/VERSION</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS</t>
+    <t>STATUS</t>
   </si>
   <si>
-    <t xml:space="preserve">PO</t>
+    <t>PO</t>
   </si>
   <si>
-    <t xml:space="preserve">RELEASE DATE</t>
+    <t>RELEASE DATE</t>
   </si>
   <si>
-    <t xml:space="preserve">NOTES</t>
+    <t>NOTES</t>
   </si>
   <si>
-    <t xml:space="preserve">Xử lý yêu cầu</t>
+    <t>Xử lý yêu cầu</t>
   </si>
   <si>
-    <t xml:space="preserve">Thanh lý</t>
+    <t>Thanh lý</t>
   </si>
   <si>
-    <t xml:space="preserve">Cho phép thanh lý từng gói dịch vụ trong cùng một phụ lục, luồng xử lý tương tự thanh lý phụ lục.</t>
+    <t>Cho phép thanh lý từng gói dịch vụ trong cùng một phụ lục, luồng xử lý tương tự thanh lý phụ lục.</t>
   </si>
   <si>
-    <t xml:space="preserve">2-Medium</t>
+    <t>2-Medium</t>
   </si>
   <si>
-    <t xml:space="preserve">Sprint 3</t>
+    <t>Sprint 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Pending</t>
+    <t>Pending</t>
   </si>
   <si>
-    <t xml:space="preserve">ThinhDD13</t>
+    <t>ThinhDD13</t>
   </si>
   <si>
-    <t xml:space="preserve">SM 2.0 thực hiện xong sẽ tích hợp</t>
+    <t>SM 2.0 thực hiện xong sẽ tích hợp</t>
   </si>
   <si>
-    <t xml:space="preserve">Báo cáo</t>
+    <t>Báo cáo</t>
   </si>
   <si>
-    <t xml:space="preserve">Báo cáo yêu cầu</t>
+    <t>Báo cáo yêu cầu</t>
   </si>
   <si>
-    <t xml:space="preserve">Hệ thống cung cấp báo cáo thống kê khảo sát/triển khai/thanh lý/nâng-hạ cấp/chuyển địa điểm theo thời gian, TTKD và nhân viên.</t>
+    <t>Hệ thống cung cấp báo cáo thống kê khảo sát/triển khai/thanh lý/nâng-hạ cấp/chuyển địa điểm theo thời gian, TTKD và nhân viên.</t>
   </si>
   <si>
-    <t xml:space="preserve">Done</t>
+    <t>Done</t>
   </si>
   <si>
-    <t xml:space="preserve">ThaoTP</t>
+    <t>ThaoTP</t>
   </si>
   <si>
-    <t xml:space="preserve">File export báo cáo hiển thị thêm trạng thái phiếu YC (Hủy, Hoàn tất, Đang xử lý…).</t>
+    <t>File export báo cáo hiển thị thêm trạng thái phiếu YC (Hủy, Hoàn tất, Đang xử lý…).</t>
   </si>
   <si>
-    <t xml:space="preserve">NgocTT - CS</t>
+    <t>NgocTT - CS</t>
   </si>
   <si>
-    <t xml:space="preserve">Chuyển địa điểm</t>
+    <t>Chuyển địa điểm</t>
   </si>
   <si>
-    <t xml:space="preserve">Thực hiện số hóa CCD dịch vụ VOICE.</t>
+    <t>Thực hiện số hóa CCD dịch vụ VOICE.</t>
   </si>
   <si>
-    <t xml:space="preserve">3-High</t>
+    <t>3-High</t>
   </si>
   <si>
-    <t xml:space="preserve">Sprint 4</t>
+    <t>Sprint 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Quannt36</t>
+    <t>Quannt36</t>
   </si>
   <si>
-    <t xml:space="preserve">Đợi release Ivoice</t>
+    <t>Đợi release Ivoice</t>
   </si>
   <si>
-    <t xml:space="preserve">Chuyển pháp nhân</t>
+    <t>Chuyển pháp nhân</t>
   </si>
   <si>
-    <t xml:space="preserve">CPN hỗ trợ change location kèm đổi pháp nhân, cho phép xuất HĐ theo vùng miền khác.</t>
+    <t>CPN hỗ trợ change location kèm đổi pháp nhân, cho phép xuất HĐ theo vùng miền khác.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sprint 1</t>
+    <t>Sprint 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Báo cáo LL</t>
+    <t>Báo cáo LL</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất báo cáo nâng/hạ cấp với đầy đủ thông tin KH, HĐ, PL, TTKD, dịch vụ, tốc độ, địa điểm, HĐ con.</t>
+    <t>Xuất báo cáo nâng/hạ cấp với đầy đủ thông tin KH, HĐ, PL, TTKD, dịch vụ, tốc độ, địa điểm, HĐ con.</t>
   </si>
   <si>
-    <t xml:space="preserve">DuongLT2</t>
+    <t>DuongLT2</t>
   </si>
   <si>
-    <t xml:space="preserve">Màn hình chi tiết phiếu hiển thị MKH nếu có profile, nếu không hiển thị N/A.</t>
+    <t>Màn hình chi tiết phiếu hiển thị MKH nếu có profile, nếu không hiển thị N/A.</t>
   </si>
   <si>
-    <t xml:space="preserve">MiNH2</t>
+    <t>MiNH2</t>
   </si>
   <si>
-    <t xml:space="preserve">Cho phép xem chi tiết dịch vụ từ các tool nghiệp vụ ngay trong chi tiết phiếu FCR.</t>
+    <t>Cho phép xem chi tiết dịch vụ từ các tool nghiệp vụ ngay trong chi tiết phiếu FCR.</t>
   </si>
   <si>
-    <t xml:space="preserve">Thực hiện yêu cầu</t>
+    <t>Thực hiện yêu cầu</t>
   </si>
   <si>
-    <t xml:space="preserve">Bổ sung CC email và gửi mail theo các mốc xử lý của phiếu.</t>
+    <t>Bổ sung CC email và gửi mail theo các mốc xử lý của phiếu.</t>
   </si>
   <si>
-    <t xml:space="preserve">TienLTT3</t>
+    <t>TienLTT3</t>
   </si>
   <si>
-    <t xml:space="preserve">Cho phép CPN sang số HĐ VOICE đã tồn tại để tránh phải thanh lý - triển khai lại gây downtime.</t>
+    <t>Cho phép CPN sang số HĐ VOICE đã tồn tại để tránh phải thanh lý - triển khai lại gây downtime.</t>
   </si>
   <si>
-    <t xml:space="preserve">HangBT13</t>
+    <t>HangBT13</t>
   </si>
   <si>
-    <t xml:space="preserve">Thanh lý offnet</t>
+    <t>Thanh lý offnet</t>
   </si>
   <si>
-    <t xml:space="preserve">Số hóa thanh lý kênh truyền offnet toàn trình; nếu không toàn trình thì tạo phiếu BMO.</t>
+    <t>Số hóa thanh lý kênh truyền offnet toàn trình; nếu không toàn trình thì tạo phiếu BMO.</t>
   </si>
   <si>
-    <t xml:space="preserve">Đợi release LL</t>
+    <t>Đợi release LL</t>
   </si>
   <si>
-    <t xml:space="preserve">Nâng cấp/Hạ Cấp</t>
+    <t>Nâng cấp/Hạ Cấp</t>
   </si>
   <si>
-    <t xml:space="preserve">Hỗ trợ nâng/hạ cấp dịch vụ HigioCloud.</t>
+    <t>Hỗ trợ nâng/hạ cấp dịch vụ HigioCloud.</t>
   </si>
   <si>
-    <t xml:space="preserve">Chaulm9</t>
+    <t>Chaulm9</t>
   </si>
   <si>
-    <t xml:space="preserve">Đợi release SM v2.0</t>
+    <t>Đợi release SM v2.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Xử lý yêu cầu nghiệp vụ</t>
+    <t>Xử lý yêu cầu nghiệp vụ</t>
   </si>
   <si>
-    <t xml:space="preserve">Phân biệt nâng/hạ cấp tạm thời và chính thức để áp dụng luồng duyệt phù hợp, kèm nhắc nợ hồ sơ.</t>
+    <t>Phân biệt nâng/hạ cấp tạm thời và chính thức để áp dụng luồng duyệt phù hợp, kèm nhắc nợ hồ sơ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Thay đổi thông tin dịch vụ</t>
+    <t>Thay đổi thông tin dịch vụ</t>
   </si>
   <si>
-    <t xml:space="preserve">Chuyển chức năng thay đổi thông tin dịch vụ từ SM sang FCR.</t>
+    <t>Chuyển chức năng thay đổi thông tin dịch vụ từ SM sang FCR.</t>
   </si>
   <si>
-    <t xml:space="preserve">1-Low</t>
+    <t>1-Low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quản lý tài liệu đính kèm</t>
+    <t>Quản lý tài liệu đính kèm</t>
   </si>
   <si>
-    <t xml:space="preserve">Đính kèm tài liệu</t>
+    <t>Đính kèm tài liệu</t>
   </si>
   <si>
-    <t xml:space="preserve">Đính kèm tài liệu ở các bước duyệt &amp; đồng bộ CM.</t>
+    <t>Đính kèm tài liệu ở các bước duyệt &amp; đồng bộ CM.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sprint 2</t>
+    <t>Sprint 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Tạo yêu cầu</t>
+    <t>Tạo yêu cầu</t>
   </si>
   <si>
-    <t xml:space="preserve">Người tạo phiếu được nhập ngày hiệu lực, điều khoản đối soát, chu kỳ thanh toán, và hình thức thanh toán (trả trước/trả sau).</t>
+    <t>Người tạo phiếu được nhập ngày hiệu lực, điều khoản đối soát, chu kỳ thanh toán, và hình thức thanh toán (trả trước/trả sau).</t>
   </si>
   <si>
-    <t xml:space="preserve">TrangLTH52</t>
+    <t>TrangLTH52</t>
   </si>
   <si>
-    <t xml:space="preserve">Next version</t>
+    <t>Next version</t>
   </si>
   <si>
-    <t xml:space="preserve">Cho phép tạo/duyệt/xử lý YCTL cho HĐ/PL đã cấp số nhưng chưa triển khai.</t>
+    <t>Cho phép tạo/duyệt/xử lý YCTL cho HĐ/PL đã cấp số nhưng chưa triển khai.</t>
   </si>
   <si>
-    <t xml:space="preserve">Thanh lý Ivoice</t>
+    <t>Thanh lý Ivoice</t>
   </si>
   <si>
-    <t xml:space="preserve">Không chặn duyệt YCTL của CSM khi HĐ còn phiếu tồn.</t>
+    <t>Không chặn duyệt YCTL của CSM khi HĐ còn phiếu tồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Gia hạn IDC</t>
+    <t>Gia hạn IDC</t>
   </si>
   <si>
-    <t xml:space="preserve">Điều chỉnh rule: không chặn mở gông, cho phép tồn NC/HC/CPN vẫn tạo gia hạn.</t>
+    <t>Điều chỉnh rule: không chặn mở gông, cho phép tồn NC/HC/CPN vẫn tạo gia hạn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Tìm kiếm</t>
+    <t>Tìm kiếm</t>
   </si>
   <si>
-    <t xml:space="preserve">Danh sách yêu cầu</t>
+    <t>Danh sách yêu cầu</t>
   </si>
   <si>
-    <t xml:space="preserve">Cho phép search và truy cập phiếu liên phòng ban, không giới hạn theo account đã duyệt.</t>
+    <t>Cho phép search và truy cập phiếu liên phòng ban, không giới hạn theo account đã duyệt.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cancel</t>
+    <t>Cancel</t>
   </si>
   <si>
-    <t xml:space="preserve">Vyntt30</t>
+    <t>Vyntt30</t>
   </si>
   <si>
-    <t xml:space="preserve">Tìm kiếm yêu cầu</t>
+    <t>Tìm kiếm yêu cầu</t>
   </si>
   <si>
-    <t xml:space="preserve">Tại màn hình chính FCR, search phiếu bằng kính lúp + Enter và điều hướng trực tiếp vào chi tiết phiếu.</t>
+    <t>Tại màn hình chính FCR, search phiếu bằng kính lúp + Enter và điều hướng trực tiếp vào chi tiết phiếu.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cải tiến SLA</t>
+    <t>Cải tiến SLA</t>
   </si>
   <si>
-    <t xml:space="preserve">SLA - Pending AF</t>
+    <t>SLA - Pending AF</t>
   </si>
   <si>
-    <t xml:space="preserve">Pending SLA tại bước AF Công nợ, không tính SLA khi pending.</t>
+    <t>Pending SLA tại bước AF Công nợ, không tính SLA khi pending.</t>
   </si>
   <si>
-    <t xml:space="preserve">SLA - Giờ hành chính, ngày lễ</t>
+    <t>SLA - Giờ hành chính, ngày lễ</t>
   </si>
   <si>
-    <t xml:space="preserve">Phiếu tạo sau 17h30 tính SLA từ ngày làm việc kế tiếp, ngày lễ</t>
+    <t>Phiếu tạo sau 17h30 tính SLA từ ngày làm việc kế tiếp, ngày lễ</t>
   </si>
   <si>
-    <t xml:space="preserve">Hệ thống hỗ trợ ưu tiên xử lý khi có nhiều phiếu NC và HC.</t>
+    <t>Hệ thống hỗ trợ ưu tiên xử lý khi có nhiều phiếu NC và HC.</t>
   </si>
   <si>
-    <t xml:space="preserve">MinhNTT7</t>
+    <t>MinhNTT7</t>
   </si>
   <si>
-    <t xml:space="preserve">Điều chỉnh backdate các phiếu yêu cầu</t>
+    <t>Điều chỉnh backdate các phiếu yêu cầu</t>
   </si>
   <si>
-    <t xml:space="preserve">Phân quyền &amp; Quy trình</t>
+    <t>Phân quyền &amp; Quy trình</t>
   </si>
   <si>
-    <t xml:space="preserve">Cài đặt</t>
+    <t>Cài đặt</t>
   </si>
   <si>
-    <t xml:space="preserve">Role QA publish quy trình không cần qua bước duyệt.</t>
+    <t>Role QA publish quy trình không cần qua bước duyệt.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cho phép tiếp tục thực hiện phiếu tại bước từ chối thay vì đi lại luồng từ đầu</t>
+    <t>Cho phép tiếp tục thực hiện phiếu tại bước từ chối thay vì đi lại luồng từ đầu</t>
   </si>
   <si>
-    <t xml:space="preserve">DatPTQ</t>
+    <t>DatPTQ</t>
   </si>
   <si>
-    <t xml:space="preserve">Cải tiến tạo/chỉnh sửa phiếu</t>
+    <t>Cải tiến tạo/chỉnh sửa phiếu</t>
   </si>
   <si>
-    <t xml:space="preserve">Backdate phiếu</t>
+    <t>Backdate phiếu</t>
   </si>
   <si>
-    <t xml:space="preserve">Cho phép backdate phiếu CPN/NCHC/TLTN/GH khi tạo/chỉnh sửa.</t>
+    <t>Cho phép backdate phiếu CPN/NCHC/TLTN/GH khi tạo/chỉnh sửa.</t>
   </si>
   <si>
-    <t xml:space="preserve">CPN - Load loại HĐ</t>
+    <t>CPN - Load loại HĐ</t>
   </si>
   <si>
-    <t xml:space="preserve">Tạo phiếu CPN số mới tự động load loại HĐ theo HĐ cũ.</t>
+    <t>Tạo phiếu CPN số mới tự động load loại HĐ theo HĐ cũ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Quản lý mã triển khai</t>
+    <t>Quản lý mã triển khai</t>
   </si>
   <si>
-    <t xml:space="preserve">Đồng bộ dữ liệu</t>
+    <t>Đồng bộ dữ liệu</t>
   </si>
   <si>
-    <t xml:space="preserve">Thông tin MTK trên CM hiển thị thêm cột "Loại dịch vụ", trạng thái base theo LL.</t>
+    <t>Thông tin MTK trên CM hiển thị thêm cột "Loại dịch vụ", trạng thái base theo LL.</t>
   </si>
   <si>
-    <t xml:space="preserve">AnhNTC2</t>
+    <t>AnhNTC2</t>
   </si>
   <si>
-    <t xml:space="preserve">Thực hiện sau CM 3.0</t>
+    <t>Thực hiện sau CM 3.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Trạng thái mới</t>
+    <t>Trạng thái mới</t>
   </si>
   <si>
-    <t xml:space="preserve">LL bổ sung trạng thái triển khai "Triển khai lần đầu không thành công" và FCR không cho phép tạo phiếu với trạng thái này.</t>
+    <t>LL bổ sung trạng thái triển khai "Triển khai lần đầu không thành công" và FCR không cho phép tạo phiếu với trạng thái này.</t>
   </si>
   <si>
-    <t xml:space="preserve">Email</t>
+    <t>Email</t>
   </si>
   <si>
-    <t xml:space="preserve">Gửi mail thông báo</t>
+    <t>Gửi mail thông báo</t>
   </si>
   <si>
-    <t xml:space="preserve">Bổ sung vùng miền HĐ, phiếu thay đổi thông tin có phân biệt tạm thời hay chính thức.</t>
+    <t>Bổ sung vùng miền HĐ, phiếu thay đổi thông tin có phân biệt tạm thời hay chính thức.</t>
   </si>
   <si>
-    <t xml:space="preserve">NamDP</t>
+    <t>NamDP</t>
   </si>
   <si>
-    <t xml:space="preserve">Thanh lý ivoice</t>
+    <t>Thanh lý ivoice</t>
   </si>
   <si>
-    <t xml:space="preserve">Bổ sung cảnh báo phát sinh cước cho phiếu tạo sang ngày 20.</t>
+    <t>Bổ sung cảnh báo phát sinh cước cho phiếu tạo sang ngày 20.</t>
   </si>
   <si>
-    <t xml:space="preserve">Gộp quy trình NC, HC thành Thay đổi thông tin dịch vụ.</t>
+    <t>Gộp quy trình NC, HC thành Thay đổi thông tin dịch vụ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Đối với CSKH, bổ sung thêm bước SCS confirm (thanh lý với NCC).</t>
+    <t>Đối với CSKH, bổ sung thêm bước SCS confirm (thanh lý với NCC).</t>
   </si>
   <si>
-    <t xml:space="preserve">Thực hiện trong version Ivoice</t>
+    <t>Thực hiện trong version Ivoice</t>
   </si>
   <si>
-    <t xml:space="preserve">Nâng cấp - Linh hoạt NIX/GIA và Bảng thông số dịch vụ</t>
+    <t>Nâng cấp - Linh hoạt NIX/GIA và Bảng thông số dịch vụ</t>
   </si>
   <si>
-    <t xml:space="preserve">Thay đổi thông tin</t>
+    <t>Thay đổi thông tin</t>
   </si>
   <si>
-    <t xml:space="preserve">Cải tiến luồng thay đổi: bỏ ràng buộc nhập đồng thời NIX/GIA, chỉ validate BW NIX khi nâng, hiển thị bảng thông số động theo loại và xử lý cảnh báo MTK</t>
+    <t>Cải tiến luồng thay đổi: bỏ ràng buộc nhập đồng thời NIX/GIA, chỉ validate BW NIX khi nâng, hiển thị bảng thông số động theo loại và xử lý cảnh báo MTK</t>
   </si>
   <si>
-    <t xml:space="preserve">VyPTL</t>
+    <t>VyPTL</t>
   </si>
   <si>
-    <t xml:space="preserve">Xử lý yêu cầu - CPN</t>
+    <t>Xử lý yêu cầu - CPN</t>
   </si>
   <si>
-    <t xml:space="preserve">Chuyển Pháp Nhân</t>
+    <t>Chuyển Pháp Nhân</t>
   </si>
   <si>
-    <t xml:space="preserve">Mở rộng CPN hỗ trợ hợp đồng Tạm ngưng (nguyên nhân không phải cước) và CPN toàn phần (giữ/đổi số HĐ, auto resume khi gia hạn)</t>
+    <t>Mở rộng CPN hỗ trợ hợp đồng Tạm ngưng (nguyên nhân không phải cước) và CPN toàn phần (giữ/đổi số HĐ, auto resume khi gia hạn)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hiển thị đầy đủ thông tin hợp đồng trong CPN, đồng bộ CM, hỗ trợ hyperlink và filter loại yêu cầu/dịch vụ</t>
+    <t>Hiển thị đầy đủ thông tin hợp đồng trong CPN, đồng bộ CM, hỗ trợ hyperlink và filter loại yêu cầu/dịch vụ</t>
   </si>
   <si>
-    <t xml:space="preserve">Nâng giới hạn dung lượng file đính kèm trong yêu cầu CPN từ 5MB lên 25MB</t>
+    <t>Nâng giới hạn dung lượng file đính kèm trong yêu cầu CPN từ 5MB lên 25MB</t>
   </si>
   <si>
-    <t xml:space="preserve">AnhNTC</t>
+    <t>AnhNTC</t>
   </si>
   <si>
-    <t xml:space="preserve">Báo cáo theo loại yêu cầu</t>
+    <t>Báo cáo theo loại yêu cầu</t>
   </si>
   <si>
-    <t xml:space="preserve">Thêm filter động theo loại yêu cầu/dịch vụ, default ngày tạo phiếu, hiển thị NA cho dịch vụ kênh</t>
+    <t>Thêm filter động theo loại yêu cầu/dịch vụ, default ngày tạo phiếu, hiển thị NA cho dịch vụ kênh</t>
   </si>
   <si>
-    <t xml:space="preserve">Thay đổi thông tin - Ngày đề nghị</t>
+    <t>Thay đổi thông tin - Ngày đề nghị</t>
   </si>
   <si>
-    <t xml:space="preserve">Load mặc định trường Ngày đề nghị, cập nhật validation và database schema tương ứng</t>
+    <t>Load mặc định trường Ngày đề nghị, cập nhật validation và database schema tương ứng</t>
   </si>
   <si>
-    <t xml:space="preserve">SPRINT BACKLOG #4</t>
+    <t>SPRINT BACKLOG #4</t>
   </si>
   <si>
-    <t xml:space="preserve">SPRINT GOAL</t>
+    <t>SPRINT GOAL</t>
   </si>
   <si>
-    <t xml:space="preserve">Hoàn thiện nghiệp vụ thay đổi thông tin LL (bỏ ràng buộc NIX/GIA), mở rộng CPN hỗ trợ hợp đồng Tạm ngưng, cải tiến Báo cáo SLA có filter động, bỏ trường Ngày đề nghị trong Thay đổi thông tin, và nâng giới hạn đính kèm file.</t>
+    <t>Hoàn thiện nghiệp vụ thay đổi thông tin LL (bỏ ràng buộc NIX/GIA), mở rộng CPN hỗ trợ hợp đồng Tạm ngưng, cải tiến Báo cáo SLA có filter động, bỏ trường Ngày đề nghị trong Thay đổi thông tin, và nâng giới hạn đính kèm file.</t>
   </si>
   <si>
-    <t xml:space="preserve">STORY POINT OF THIS SPRINT</t>
+    <t>STORY POINT OF THIS SPRINT</t>
   </si>
   <si>
-    <t xml:space="preserve">MANDAY</t>
+    <t>MANDAY</t>
   </si>
   <si>
-    <t xml:space="preserve">TIME BOX</t>
+    <t>TIME BOX</t>
   </si>
   <si>
     <t xml:space="preserve">1. Sprint Timeline: 08/06/2026 – 22/07/2026
@@ -556,7 +556,7 @@
 ID</t>
   </si>
   <si>
-    <t xml:space="preserve">MODULE/ FEATURE</t>
+    <t>MODULE/ FEATURE</t>
   </si>
   <si>
     <t xml:space="preserve">STORY
@@ -569,16 +569,16 @@
 Manday)</t>
   </si>
   <si>
-    <t xml:space="preserve">Priority</t>
+    <t>Priority</t>
   </si>
   <si>
-    <t xml:space="preserve">Complexity</t>
+    <t>Complexity</t>
   </si>
   <si>
-    <t xml:space="preserve">TASK</t>
+    <t>TASK</t>
   </si>
   <si>
-    <t xml:space="preserve">PIC</t>
+    <t>PIC</t>
   </si>
   <si>
     <t xml:space="preserve">ESTIMATED
@@ -587,10 +587,10 @@
 Manday)</t>
   </si>
   <si>
-    <t xml:space="preserve">START DATE</t>
+    <t>START DATE</t>
   </si>
   <si>
-    <t xml:space="preserve">DUE DATE</t>
+    <t>DUE DATE</t>
   </si>
   <si>
     <t xml:space="preserve">WORKING
@@ -602,287 +602,193 @@
 (HOUR)</t>
   </si>
   <si>
-    <t xml:space="preserve">TASK COMPLEXITY</t>
+    <t>TASK COMPLEXITY</t>
   </si>
   <si>
-    <t xml:space="preserve">Type OF WORK</t>
+    <t>Type OF WORK</t>
   </si>
   <si>
-    <t xml:space="preserve">TASK PROCESS</t>
+    <t>TASK PROCESS</t>
   </si>
   <si>
-    <t xml:space="preserve">TASK PRIORITY</t>
+    <t>TASK PRIORITY</t>
   </si>
   <si>
-    <t xml:space="preserve">EPIC-0. Init Sprint - Kick-off, Analysis &amp; Setup</t>
+    <t>EPIC-0. Init Sprint - Kick-off, Analysis &amp; Setup</t>
   </si>
   <si>
-    <t xml:space="preserve">US_0.1</t>
+    <t>US_0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Project Management</t>
+    <t>Project Management</t>
   </si>
   <si>
-    <t xml:space="preserve">Initiation &amp; Risk Management - Kick-off Sprint, lập kế hoạch và theo dõi rủi ro</t>
+    <t>Initiation &amp; Risk Management - Kick-off Sprint, lập kế hoạch và theo dõi rủi ro</t>
   </si>
   <si>
-    <t xml:space="preserve">Sprint 4 Kick-off &amp; Planning - Risk tracking</t>
+    <t>Sprint 4 Kick-off &amp; Planning - Risk tracking</t>
   </si>
   <si>
-    <t xml:space="preserve">DuyVM4</t>
+    <t>DuyVM4</t>
   </si>
   <si>
-    <t xml:space="preserve">Not Started</t>
+    <t>Not Started</t>
   </si>
   <si>
-    <t xml:space="preserve">Do</t>
+    <t>Do</t>
   </si>
   <si>
-    <t xml:space="preserve">Medium</t>
+    <t>Medium</t>
   </si>
   <si>
-    <t xml:space="preserve">Phân tích toàn bộ User Stories, thiết kế wireframe và viết URD</t>
+    <t>Phân tích toàn bộ User Stories, thiết kế wireframe và viết URD</t>
   </si>
   <si>
-    <t xml:space="preserve">OanhNTK35</t>
+    <t>OanhNTK35</t>
   </si>
   <si>
-    <t xml:space="preserve">BA phân tích toàn bộ User Stories Sprint 4, thiết kế wireframe và viết URD trước khi DEV bắt đầu coding</t>
+    <t>BA phân tích toàn bộ User Stories Sprint 4, thiết kế wireframe và viết URD trước khi DEV bắt đầu coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Requirement &amp; Design</t>
+    <t>Requirement &amp; Design</t>
   </si>
   <si>
-    <t xml:space="preserve">US_0.2</t>
+    <t>US_0.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Development Setup</t>
+    <t>Development Setup</t>
   </si>
   <si>
-    <t xml:space="preserve">Setup môi trường, review hệ thống hiện tại, phân tích technical design và refactor codebase trước khi implement</t>
+    <t>Setup môi trường, review hệ thống hiện tại, phân tích technical design và refactor codebase trước khi implement</t>
   </si>
   <si>
-    <t xml:space="preserve">Setup local env, đọc spec, align với BA trước khi coding</t>
+    <t>Setup local env, đọc spec, align với BA trước khi coding</t>
   </si>
   <si>
-    <t xml:space="preserve">NguyenHVN2</t>
+    <t>NguyenHVN2</t>
   </si>
   <si>
-    <t xml:space="preserve">Setup môi trường dev &amp; đọc spec Sprint 4</t>
+    <t>Setup môi trường dev &amp; đọc spec Sprint 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Review</t>
+    <t>Review</t>
   </si>
   <si>
-    <t xml:space="preserve">Review hệ thống FCR - đọc code &amp; hiểu luồng BW hiện tại</t>
+    <t>Review hệ thống FCR - đọc code &amp; hiểu luồng BW hiện tại</t>
   </si>
   <si>
-    <t xml:space="preserve">Rà soát codebase module Nâng cấp BW, ghi nhận technical debt và chuẩn bị cho triển khai Sprint 4</t>
+    <t>Rà soát codebase module Nâng cấp BW, ghi nhận technical debt và chuẩn bị cho triển khai Sprint 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Setup local env, đọc spec CPN, align với BA</t>
+    <t>Setup local env, đọc spec CPN, align với BA</t>
   </si>
   <si>
-    <t xml:space="preserve">ThangDQ16</t>
+    <t>ThangDQ16</t>
   </si>
   <si>
-    <t xml:space="preserve">Review hệ thống FCR - đọc code &amp; hiểu luồng CPN hiện tại</t>
+    <t>Review hệ thống FCR - đọc code &amp; hiểu luồng CPN hiện tại</t>
   </si>
   <si>
-    <t xml:space="preserve">Review code base module CPN, ghi nhận state machine HĐ, API CM hiện tại</t>
+    <t>Review code base module CPN, ghi nhận state machine HĐ, API CM hiện tại</t>
   </si>
   <si>
-    <t xml:space="preserve">Phân tích technical design - Nâng cấp BW NIX/GIA</t>
+    <t>Phân tích technical design - Nâng cấp BW NIX/GIA</t>
   </si>
   <si>
-    <t xml:space="preserve">Nghiên cứu luồng nghiệp vụ CPN &amp; phân tích DB schema</t>
+    <t>Nghiên cứu luồng nghiệp vụ CPN &amp; phân tích DB schema</t>
   </si>
   <si>
-    <t xml:space="preserve">Refactor module Nâng cấp BW - Clean code &amp; chuẩn bị base Sprint 4 - Tuần 1</t>
+    <t>Refactor module Nâng cấp BW - Clean code &amp; chuẩn bị base Sprint 4 - Tuần 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Fix/Rework</t>
+    <t>Fix/Rework</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding</t>
+    <t>Coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Refactor module CPN - Clean code &amp; chuẩn bị base Sprint 4 - Tuần 1</t>
+    <t>Refactor module CPN - Clean code &amp; chuẩn bị base Sprint 4 - Tuần 1</t>
   </si>
   <si>
-    <t xml:space="preserve">EPIC-1. Nâng cấp - Linh hoạt NIX/GIA và Bảng thông số dịch vụ</t>
+    <t>EPIC-1. Nâng cấp - Linh hoạt NIX/GIA và Bảng thông số dịch vụ</t>
   </si>
   <si>
-    <t xml:space="preserve">US_1.1</t>
+    <t>US_1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Cải tiến luồng thay đổi: bỏ ràng buộc nhập đồng thời NIX/GIA, chỉ validate BW NIX khi nâng, hiển thị bảng thông số động theo loại và xử lý cảnh báo MTK.</t>
+    <t>Cải tiến luồng thay đổi: bỏ ràng buộc nhập đồng thời NIX/GIA, chỉ validate BW NIX khi nâng, hiển thị bảng thông số động theo loại và xử lý cảnh báo MTK.</t>
   </si>
   <si>
-    <t xml:space="preserve">Implement logic validate linh hoạt NIX/GIA - bỏ ràng buộc bắt buộc nhập cả 2, chỉ validate BW NIX khi thực sự nâng NIX</t>
+    <t>Implement logic validate linh hoạt NIX/GIA - bỏ ràng buộc bắt buộc nhập cả 2, chỉ validate BW NIX khi thực sự nâng NIX</t>
   </si>
   <si>
-    <t xml:space="preserve">Tham chiếu ví dụ DNL00038: BW 60-100 chỉ nâng GIA, không bắt buộc NIX</t>
+    <t>Tham chiếu ví dụ DNL00038: BW 60-100 chỉ nâng GIA, không bắt buộc NIX</t>
   </si>
   <si>
-    <t xml:space="preserve">High</t>
+    <t>High</t>
   </si>
   <si>
-    <t xml:space="preserve">Implement hiển thị Bảng thông số dịch vụ động theo loại (GIA only, NIX only, Peering, GIA-NIX kết hợp)</t>
+    <t>Implement hiển thị Bảng thông số dịch vụ động theo loại (GIA only, NIX only, Peering, GIA-NIX kết hợp)</t>
   </si>
   <si>
-    <t xml:space="preserve">5 loại cấu hình: GIA only, NIX only, Peering, GIA-NIX, kết hợp khác</t>
+    <t>5 loại cấu hình: GIA only, NIX only, Peering, GIA-NIX, kết hợp khác</t>
   </si>
   <si>
-    <t xml:space="preserve">Implement cảnh báo và form xử lý trường hợp Nâng cấp có MTK (không bắt buộc nhập theo hướng dẫn riêng)</t>
+    <t>Implement cảnh báo và form xử lý trường hợp Nâng cấp có MTK (không bắt buộc nhập theo hướng dẫn riêng)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hiển thị popup hướng dẫn khi MTK không được nhập; không block luồng</t>
+    <t>Hiển thị popup hướng dẫn khi MTK không được nhập; không block luồng</t>
   </si>
   <si>
-    <t xml:space="preserve">US_1.2</t>
+    <t>US_1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit test cho toàn bộ logic validate NIX/GIA linh hoạt và bảng thông số dịch vụ, đảm bảo không xảy ra regression với các luồng.</t>
+    <t>Unit test cho toàn bộ logic validate NIX/GIA linh hoạt và bảng thông số dịch vụ, đảm bảo không xảy ra regression với các luồng.</t>
   </si>
   <si>
-    <t xml:space="preserve">Viết unit test cho logic validate linh hoạt NIX/GIA và bảng thông số dịch vụ</t>
+    <t>Viết unit test cho logic validate linh hoạt NIX/GIA và bảng thông số dịch vụ</t>
   </si>
   <si>
-    <t xml:space="preserve">Coverage tối thiểu 80%; bao gồm edge case BW NIX = BW hiện tại</t>
+    <t>Coverage tối thiểu 80%; bao gồm edge case BW NIX = BW hiện tại</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit Test</t>
+    <t>Unit Test</t>
   </si>
   <si>
-    <t xml:space="preserve">STORY POINT GUIDELINE</t>
+    <t>STORY POINT GUIDELINE</t>
   </si>
   <si>
-    <t xml:space="preserve">Công thức Story Point</t>
+    <t>Công thức Story Point</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFC65911"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Trung bình cộng</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> 3 cột: </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tổng</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Manday của User Story</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Priority*2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Complexity*2</t>
-    </r>
+    <t>Trung bình cộng 3 cột: Tổng Manday của User Story, Priority*2, Complexity*2</t>
   </si>
   <si>
-    <t xml:space="preserve">Tổng Manday của User Story</t>
+    <t>Tổng Manday của User Story</t>
   </si>
   <si>
-    <t xml:space="preserve">Tổng manday của tất cả các task trong User Story đó</t>
+    <t>Tổng manday của tất cả các task trong User Story đó</t>
   </si>
   <si>
-    <t xml:space="preserve">Mức độ cấp thiết của User Story</t>
+    <t>Mức độ cấp thiết của User Story</t>
   </si>
   <si>
-    <t xml:space="preserve">4-Critical</t>
+    <t>4-Critical</t>
   </si>
   <si>
-    <t xml:space="preserve">Các yêu cầu chen ngang cần thực hiện gấp (theo chỉ đạo từ BĐH, BGĐ…)</t>
+    <t>Các yêu cầu chen ngang cần thực hiện gấp (theo chỉ đạo từ BĐH, BGĐ…)</t>
   </si>
   <si>
-    <t xml:space="preserve">Must have - chức năng quan trọng và nhất định phải có trong Sprint</t>
+    <t>Must have - chức năng quan trọng và nhất định phải có trong Sprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Should have - quan trọng nhưng không gấp, có thể khó chịu nếu loại bỏ nhưng giải pháp vẫn còn khả thi</t>
+    <t>Should have - quan trọng nhưng không gấp, có thể khó chịu nếu loại bỏ nhưng giải pháp vẫn còn khả thi</t>
   </si>
   <si>
-    <t xml:space="preserve">Could have - muốn hoặc kỳ vọng có nhưng không quan trọng</t>
+    <t>Could have - muốn hoặc kỳ vọng có nhưng không quan trọng</t>
   </si>
   <si>
-    <t xml:space="preserve">Mức độ phức tạp của User Story</t>
+    <t>Mức độ phức tạp của User Story</t>
   </si>
   <si>
     <t xml:space="preserve">- Liên đới nhiều hơn 3 Function, Story khác 
@@ -2971,7 +2877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -9957,7 +9863,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -11034,7 +10940,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <tabColor rgb="FF1E4E79"/>
     <pageSetUpPr fitToPage="true"/>
@@ -21147,7 +21053,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -23203,7 +23109,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
